--- a/data/batches/B05_Events_AE_DS_MH_DV/Test_Validation_Report/Test_Validation_Report_B05.xlsx
+++ b/data/batches/B05_Events_AE_DS_MH_DV/Test_Validation_Report/Test_Validation_Report_B05.xlsx
@@ -869,7 +869,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -920,7 +920,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>FAIL - Domain mismatch</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -13049,11 +13049,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-FRA_SITE01-0013</t>
-        </is>
-      </c>
+      <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
           <t>AEBODSYS</t>
@@ -13080,11 +13076,7 @@
           <t>INCONSISTENT BODSYS</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>Gastrointestinal disorders</t>
-        </is>
-      </c>
+      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13107,7 +13099,7 @@
       </c>
       <c r="Q136" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -13132,11 +13124,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>MS200095-0022-VISION-USA_SITE02-0002</t>
-        </is>
-      </c>
+      <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
           <t>AEDECOD</t>
@@ -13163,11 +13151,7 @@
           <t>INCONSISTENT TERM</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>Oedema peripheral</t>
-        </is>
-      </c>
+      <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -13190,7 +13174,7 @@
       </c>
       <c r="Q137" t="inlineStr">
         <is>
-          <t>Original or dirty value mismatch</t>
+          <t>Duplicate with mutation mismatch</t>
         </is>
       </c>
     </row>
@@ -13487,7 +13471,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=2</t>
+          <t>Complete Row @ CSV Row 3; count=1</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -13497,17 +13481,17 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-CHN_SITE01-0001; count=3</t>
+          <t>Complete Row @ CSV Row 3; count=0</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -13570,7 +13554,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0004; count=2</t>
+          <t>Complete Row @ CSV Row 9; count=1</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -13580,17 +13564,17 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>USUBJID=MS200095-0022-VISION-DEU_SITE01-0004; count=3</t>
+          <t>Complete Row @ CSV Row 9; count=0</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
           <t>No</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>Yes</t>
         </is>
       </c>
       <c r="O142" t="inlineStr">
@@ -13788,11 +13772,7 @@
           <t>AE</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr">
         <is>
           <t>AEMODIFY</t>
@@ -13800,25 +13780,49 @@
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr"/>
-      <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Column not present in original</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>USUBJID not found in original or dirty CSV</t>
+          <t>New column injection verified successfully</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14488,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -14535,7 +14539,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>FAIL - Imputation mismatch</t>
+          <t>FAIL - Domain mismatch</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
